--- a/forms/trg/Formulir_TRG_eaging.xlsx
+++ b/forms/trg/Formulir_TRG_eaging.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,27 +925,31 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Kathleen Potempa, Ph.D. RN.</t>
+          <t>Dr. Rosyidah Arafat, MN., RN</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>School of Nursing, University of Michigan, USA</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-4715-7668</t>
+        </is>
+      </c>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57190430520</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -958,17 +962,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Mayumi Kato, Ph.D., RN.</t>
+          <t>Prof. Kathleen Potempa, Ph.D. RN.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Graduate School of Medical Sciences, Kanazawa University, Japan</t>
+          <t>School of Nursing, University of Michigan, USA</t>
         </is>
       </c>
       <c r="E6" s="11" t="n"/>
@@ -976,17 +980,9 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-5965-299X</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>36989192500</t>
-        </is>
-      </c>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -999,17 +995,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Sakul Changmai, Ph.D., RN.</t>
+          <t>Prof. Mayumi Kato, Ph.D., RN.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>College of Nursing, Christian University of Thailand, Thailand</t>
+          <t>Graduate School of Medical Sciences, Kanazawa University, Japan</t>
         </is>
       </c>
       <c r="E7" s="11" t="n"/>
@@ -1017,9 +1013,17 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-5965-299X</t>
+        </is>
+      </c>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>36989192500</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1032,17 +1036,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Noor Azah Abd Aziz</t>
+          <t>Sakul Changmai, Ph.D., RN.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Medicine, Universiti Kebangsaan Malaysia, Malaysia</t>
+          <t>College of Nursing, Christian University of Thailand, Thailand</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -1050,17 +1054,9 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-7204-6097</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>24074125700</t>
-        </is>
-      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1073,23 +1069,35 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Wa Ode Nur Isnah Sabriyati, RN</t>
+          <t>Prof. Dr. Noor Azah Abd Aziz</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researcher</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Faculty of Medicine, Universiti Kebangsaan Malaysia, Malaysia</t>
+        </is>
+      </c>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-7204-6097</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>24074125700</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1102,7 +1110,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Riska Nuramalia, S.Ft., Physio., M.Biomed, Ph.D</t>
+          <t>Wa Ode Nur Isnah Sabriyati, RN</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1131,7 +1139,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Fadiah Izzati Salim, S.Kep., Ns., M.Kep</t>
+          <t>Riska Nuramalia, S.Ft., Physio., M.Biomed, Ph.D</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1140,26 +1148,14 @@
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>nurisnah@unhas.ac.id</t>
-        </is>
-      </c>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-5434-682X</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>57215875965</t>
-        </is>
-      </c>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1172,27 +1168,35 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Asri Wahyuni, RN.</t>
+          <t>Fadiah Izzati Salim, S.Kep., Ns., M.Kep</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>nurisnah@unhas.ac.id</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-5434-682X</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>57215875965</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1205,12 +1209,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Normalia, RN.</t>
+          <t>Asri Wahyuni, RN.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1238,12 +1242,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Demitrius Liklao Sikone, RN.</t>
+          <t>Normalia, RN.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1269,10 +1273,22 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Demitrius Liklao Sikone, RN.</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1280,7 +1296,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1469,15 +1489,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
